--- a/data/nasdaq100_active/구성종목_2026-06-11.xlsx
+++ b/data/nasdaq100_active/구성종목_2026-06-11.xlsx
@@ -167,7 +167,7 @@
     <t>27,392,251</t>
   </si>
   <si>
-    <t>NQM6 Index</t>
+    <t>NQM6 INDEX</t>
   </si>
   <si>
     <t>NASDAQ 100 E-MINI INDEX JUN 2026</t>
